--- a/astro-site/public/dl/plan-negocio-hamburgueseria/plan-financiero-hamburgueseria.xlsx
+++ b/astro-site/public/dl/plan-negocio-hamburgueseria/plan-financiero-hamburgueseria.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Materia prima de la comida sobre sus ventas: un 28 %, el lado prudente. El escandallo teórico de la calculadora del pack sale en un 24 % de media ponderada (la smash doble con queso, en un 27 %; la ración de patatas congeladas, en un 8 %), pero la cuenta real es lo que compras frente a lo que vendes: las bolas, el pan y las salsas que se tiran al cierre suman un punto y medio; las comidas del personal, las invitaciones, los errores y las reclamaciones de la plataforma, otro punto y medio, y las promociones de la plataforma (el dos por uno, la primera compra), un punto más. La carne es un precio estimado por el kit. Mide tu consumo el primer trimestre y cambia esta celda: cada punto vale unos 3.800 € al año</t>
+          <t>Materia prima de la comida sobre sus ventas: un 28 %, el lado prudente. El escandallo teórico de la calculadora del pack sale en un 24,4 % de media ponderada (la smash doble con queso, en un 26,8 %; la ración de patatas congeladas, en un 8 %), pero la cuenta real es lo que compras frente a lo que vendes: entre la receta y la caja se pierden las bolas, el pan y las salsas que se tiran al cierre, las comidas del personal, las invitaciones, los errores y las reclamaciones de la plataforma y sus promociones (el dos por uno, la primera compra), unos 4 puntos en el caso. La carne es un precio estimado por el kit. Mide tu consumo el primer trimestre y cambia esta celda: cada punto vale unos 3.800 € al año</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ventas por PLATAFORMA con su reparto (Glovo, Just Eat, Uber Eats) sobre el total: unos 12 pedidos al día. Lo que se recoge en el local (unos 13 pedidos al día, por la web o por teléfono) NO paga comisión y no va aquí: empújalo. La hamburguesa viaja bien; las patatas, peor (cucurucho ventilado y fritas al final). Si la plataforma llegara a un tercio de las ventas, pagarías unos 12.300 € más de comisión al año</t>
+          <t>Ventas por PLATAFORMA con su reparto (Glovo, Just Eat, Uber Eats) sobre el total: unos 12 pedidos al día. Lo que se recoge en el local (unos 13 pedidos al día, por la web o por teléfono) NO paga comisión y no va aquí: empújalo. La hamburguesa viaja bien; las patatas, peor (cucurucho ventilado y fritas al final). Si la plataforma llegara al 33 % de las ventas, pagarías unos 12.300 € más de comisión al año</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>La plancha de acero (fry-top) donde se aplasta cada bola: una de 80 cm va de unos 771 a 1.399 € sin IVA según la gama; el caso cuenta una de 100 cm, más el tostador del pan. Estimación del kit</t>
+          <t>La plancha de acero (fry-top) donde se aplasta cada bola: una de 60 a 80 cm va de unos 771 a 1.399 € sin IVA según la gama; el caso cuenta una de 100 cm, más el tostador del pan. Estimación del kit</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
